--- a/Pruebas calificadas/COLEGIO-BILBAO-(IED)-501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BILBAO-(IED)-501_Ajustado_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,11 +6028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -6124,7 +6036,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,11 +6277,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -6377,7 +6285,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,11 +6526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -6630,7 +6534,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,11 +6775,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -6883,7 +6783,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,11 +7024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -7136,7 +7032,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,11 +7273,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -7389,7 +7281,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,11 +7522,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -7642,7 +7530,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7883,11 +7771,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -7895,7 +7779,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8136,11 +8020,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -8148,7 +8028,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8389,11 +8269,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -8401,7 +8277,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8642,11 +8518,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -8654,7 +8526,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8891,11 +8763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -8903,7 +8771,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9144,11 +9012,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -9156,7 +9020,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9385,11 +9249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -9397,7 +9257,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9638,11 +9498,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -9650,7 +9506,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9891,11 +9747,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -9903,7 +9755,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10132,11 +9984,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -10144,7 +9992,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10385,11 +10233,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -10397,7 +10241,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10638,11 +10482,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -10650,7 +10490,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10891,11 +10731,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -10903,7 +10739,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11140,11 +10976,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -11152,7 +10984,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11393,11 +11225,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -11405,7 +11233,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11646,11 +11474,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -11658,7 +11482,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11899,11 +11723,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -11911,7 +11731,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12152,11 +11972,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -12164,7 +11980,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12405,11 +12221,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -12417,7 +12229,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12658,11 +12470,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -12670,7 +12478,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12911,11 +12719,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -12923,7 +12727,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13164,11 +12968,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -13176,7 +12976,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13417,11 +13217,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -13429,7 +13225,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13670,11 +13466,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -13682,7 +13474,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13923,11 +13715,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -13935,7 +13723,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14176,11 +13964,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -14188,7 +13972,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14429,11 +14213,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -14441,7 +14221,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14678,11 +14458,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -14690,7 +14466,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14927,11 +14703,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -14939,7 +14711,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15180,11 +14952,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -15192,7 +14960,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15433,11 +15201,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -15445,7 +15209,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15686,11 +15450,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -15698,7 +15458,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15939,11 +15699,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -15951,7 +15707,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16192,11 +15948,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -16204,7 +15956,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16445,11 +16197,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -16457,7 +16205,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16698,11 +16446,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -16710,7 +16454,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16951,11 +16695,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -16963,7 +16703,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17204,11 +16944,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -17216,7 +16952,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17457,11 +17193,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -17469,7 +17201,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17710,11 +17442,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -17722,7 +17450,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17959,11 +17687,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -17971,7 +17695,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18212,11 +17936,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -18224,7 +17944,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18465,11 +18185,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -18477,7 +18193,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18718,11 +18434,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -18730,7 +18442,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18971,11 +18683,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -18983,7 +18691,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19224,11 +18932,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -19236,7 +18940,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19477,11 +19181,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -19489,7 +19189,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19714,11 +19414,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -19726,7 +19422,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19967,11 +19663,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -19979,7 +19671,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20220,11 +19912,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001098949</t>
@@ -20232,7 +19920,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BILBAO (IED)</t>
+          <t>COLEGIO BILBAO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
